--- a/Samples~/Demo/ConfigSource/Localization/zh-CN.xlsx
+++ b/Samples~/Demo/ConfigSource/Localization/zh-CN.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Localization" sheetId="1" r:id="Rc4544ace498643de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Localization" sheetId="1" r:id="R905ba789cea441b9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -143,7 +143,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="zh_CN_Table" displayName="zh_CN_Table" ref="A1:B72" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="zh_CN_Table" displayName="zh_CN_Table" ref="A1:B74" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="2">
     <x:tableColumn id="1" name="Key"/>
     <x:tableColumn id="2" name="Value"/>
@@ -948,10 +948,26 @@
         <x:v>中文</x:v>
       </x:c>
     </x:row>
+    <x:row r="73">
+      <x:c r="A73" t="str">
+        <x:v>UI_Restart</x:v>
+      </x:c>
+      <x:c r="B73" t="str">
+        <x:v>重新启动</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" t="str">
+        <x:v>UI_Quit</x:v>
+      </x:c>
+      <x:c r="B74" t="str">
+        <x:v>退出游戏</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4ce5a96d53b94670"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R126d834a52594cd6"/>
   </x:tableParts>
 </x:worksheet>
 </file>